--- a/LISTAS_ORDENADAS/MI/Mangueras Espatulas y Articulos de goma/LLANAS DISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MI/Mangueras Espatulas y Articulos de goma/LLANAS DISMAY.xlsx
@@ -732,14 +732,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45208.61323711034</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="24">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -782,15 +778,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21">
       <c r="C21" s="11" t="n"/>
     </row>
@@ -841,7 +828,7 @@
       </c>
       <c r="C26" s="29" t="n"/>
       <c r="D26" s="33" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="E26" s="34" t="n"/>
     </row>
@@ -852,7 +839,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29" ht="18" customHeight="1" s="24">
       <c r="A29" s="27" t="n"/>
       <c r="B29" s="27" t="n"/>
@@ -865,21 +851,15 @@
     </row>
     <row r="31" ht="16.5" customHeight="1" s="24"/>
     <row r="32" ht="16.5" customHeight="1" s="24"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
     <row r="36" ht="19.5" customHeight="1" s="24">
       <c r="A36" s="5" t="n"/>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="3" t="n"/>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="4" t="n"/>
     </row>
-    <row r="41"/>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
